--- a/public/templates/forms/A-015-IncidentClassificationSeverityMatrix-FORM.xlsx
+++ b/public/templates/forms/A-015-IncidentClassificationSeverityMatrix-FORM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -599,7 +599,7 @@
       <c r="D5" s="22" t="n"/>
       <c r="E5" s="21" t="n"/>
     </row>
-    <row r="6" ht="43.5" customHeight="1">
+    <row r="6" ht="50.5" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Classification</t>
@@ -621,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="50.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Defines the severity tiers used to classify a cybersecurity incident, the kinds of incident that fall in each tier, and the notification timing and response each tier triggers. It is the companion to the Incident Response Plan and the basis the Incident Notification &amp; Escalation Contact List works from. Scope: all incidents affecting Agency public-safety systems, including CAD, call handling, GIS, and systems reached through IDACS.</t>
@@ -635,14 +635,14 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>« Each row is one severity tier. The columns define the tier and set what it triggers. Find the tier, then read across for the response. Delete this note before publishing. »</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Each row is one severity tier, from Sev 1 (most severe) to Sev 4 (least). For each tier the columns give its definition and impact, example incidents, the notification timing it triggers, and the escalation and response protocol. Classify an incident at the highest tier that any single column matches.</t>
@@ -690,7 +690,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="74" customHeight="1">
+    <row r="18" ht="98.0" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Sev 1: Critical</t>
@@ -826,7 +826,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>[Record any local sub-tiers, and any incident types the Agency always escalates regardless of tier (for example, any suspected compromise of CJIS data). Name the authority who may change an incident's tier mid-response.]</t>
@@ -942,10 +942,10 @@
       </c>
       <c r="E42" s="14" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="66.4" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Drafter's note (internal, delete before publishing): Reference Matrix form, build-order #66 (A-015). Severity tiers ship pre-filled (Sev 1-4) as a starting structure; the agency adjusts thresholds, examples, and timing to its systems. Classification Restricted / CJIS per the Tracker: marker-and-footer only, no separate CJIS addendum (the Reference Matrix shell has no addendum slot; incident handling of IDACS-reached systems is cited in the footer). Companion to the Incident Response Plan; feeds notification timing to the Incident Notification &amp; Escalation Contact List.</t>
+          <t>Drafter's note (internal, delete before publishing): Reference Matrix form, build-order #66. Severity tiers ship pre-filled (Sev 1-4) as a starting structure; the agency adjusts thresholds, examples, and timing to its systems. Classification Restricted / CJIS per the Tracker: marker-and-footer only, no separate CJIS addendum (the Reference Matrix shell has no addendum slot; incident handling of IDACS-reached systems is cited in the footer). Companion to the Incident Response Plan; feeds notification timing to the Incident Notification &amp; Escalation Contact List.</t>
         </is>
       </c>
     </row>
@@ -982,8 +982,14 @@
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="A18:A23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Severity Tier" prompt="Select a value" type="list">
+      <formula1>"Sev 1: Critical,Sev 2: High,Sev 3: Medium,Sev 4: Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1016,7 +1022,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, notes, review schedule and revision history live on the Matrix tab.</t>
@@ -1052,7 +1058,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Severity Tier</t>
@@ -1074,7 +1080,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Definition &amp; Impact / Example Incidents</t>
@@ -1096,7 +1102,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Notification Timing</t>
@@ -1118,7 +1124,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Escalation &amp; Response Protocol</t>
@@ -1226,6 +1232,6 @@
     <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>